--- a/data/company_data.xlsx
+++ b/data/company_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="630" windowWidth="19815" windowHeight="6600" activeTab="4"/>
+    <workbookView xWindow="510" yWindow="600" windowWidth="10215" windowHeight="5835" firstSheet="4" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -15,13 +15,18 @@
     <sheet name="SpareParts" sheetId="6" r:id="rId6"/>
     <sheet name="ServiceReports" sheetId="7" r:id="rId7"/>
     <sheet name="Staff" sheetId="8" r:id="rId8"/>
+    <sheet name="SalesFieldTrips" sheetId="9" r:id="rId9"/>
+    <sheet name="EngineerFieldTrips" sheetId="10" r:id="rId10"/>
+    <sheet name="Targets" sheetId="11" r:id="rId11"/>
+    <sheet name="HrTasks" sheetId="12" r:id="rId12"/>
+    <sheet name="AssetIssuance" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="295">
   <si>
     <t>id</t>
   </si>
@@ -428,6 +433,9 @@
     <t>3380000</t>
   </si>
   <si>
+    <t>Brian</t>
+  </si>
+  <si>
     <t>cash</t>
   </si>
   <si>
@@ -455,9 +463,6 @@
     <t>950000</t>
   </si>
   <si>
-    <t>Brian</t>
-  </si>
-  <si>
     <t>Cash</t>
   </si>
   <si>
@@ -518,96 +523,96 @@
     <t>6_months</t>
   </si>
   <si>
+    <t>sale_id</t>
+  </si>
+  <si>
+    <t>installment_number</t>
+  </si>
+  <si>
+    <t>due_date</t>
+  </si>
+  <si>
+    <t>amount_due</t>
+  </si>
+  <si>
+    <t>paid_date</t>
+  </si>
+  <si>
+    <t>payment_date</t>
+  </si>
+  <si>
+    <t>balance_after</t>
+  </si>
+  <si>
+    <t>INST-001</t>
+  </si>
+  <si>
+    <t>2026-06-30 00:00:00</t>
+  </si>
+  <si>
+    <t>Paid</t>
+  </si>
+  <si>
+    <t>INST-002</t>
+  </si>
+  <si>
+    <t>2026-08-03 00:00:00</t>
+  </si>
+  <si>
+    <t>380000</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>part_name</t>
+  </si>
+  <si>
+    <t>removed_from_item</t>
+  </si>
+  <si>
+    <t>installed_into_item</t>
+  </si>
+  <si>
+    <t>date_moved</t>
+  </si>
+  <si>
+    <t>logged_by</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>SP-001</t>
+  </si>
+  <si>
+    <t>SN8720</t>
+  </si>
+  <si>
+    <t>2026-07-26 00:00:00</t>
+  </si>
+  <si>
+    <t>testing</t>
+  </si>
+  <si>
+    <t>SP-3A423BF8</t>
+  </si>
+  <si>
+    <t>air pump</t>
+  </si>
+  <si>
+    <t>SN3421</t>
+  </si>
+  <si>
+    <t>SN0986</t>
+  </si>
+  <si>
+    <t>SN4563</t>
+  </si>
+  <si>
     <t>Maintenance</t>
   </si>
   <si>
-    <t>sale_id</t>
-  </si>
-  <si>
-    <t>installment_number</t>
-  </si>
-  <si>
-    <t>due_date</t>
-  </si>
-  <si>
-    <t>amount_due</t>
-  </si>
-  <si>
-    <t>paid_date</t>
-  </si>
-  <si>
-    <t>payment_date</t>
-  </si>
-  <si>
-    <t>balance_after</t>
-  </si>
-  <si>
-    <t>INST-001</t>
-  </si>
-  <si>
-    <t>2026-06-30 00:00:00</t>
-  </si>
-  <si>
-    <t>Paid</t>
-  </si>
-  <si>
-    <t>INST-002</t>
-  </si>
-  <si>
-    <t>2026-08-03 00:00:00</t>
-  </si>
-  <si>
-    <t>380000</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>part_name</t>
-  </si>
-  <si>
-    <t>removed_from_item</t>
-  </si>
-  <si>
-    <t>installed_into_item</t>
-  </si>
-  <si>
-    <t>date_moved</t>
-  </si>
-  <si>
-    <t>logged_by</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>SP-001</t>
-  </si>
-  <si>
-    <t>SN8720</t>
-  </si>
-  <si>
-    <t>2026-07-26 00:00:00</t>
-  </si>
-  <si>
-    <t>testing</t>
-  </si>
-  <si>
-    <t>SP-3A423BF8</t>
-  </si>
-  <si>
-    <t>air pump</t>
-  </si>
-  <si>
-    <t>SN3421</t>
-  </si>
-  <si>
-    <t>SN0986</t>
-  </si>
-  <si>
-    <t>SN4563</t>
-  </si>
-  <si>
     <t>Moved into a blood pressure machine and sold to a client.</t>
   </si>
   <si>
@@ -653,6 +658,12 @@
     <t>+256700000001</t>
   </si>
   <si>
+    <t>alvarez89@email.com</t>
+  </si>
+  <si>
+    <t>2020-11-02 00:00:00</t>
+  </si>
+  <si>
     <t>ST-2</t>
   </si>
   <si>
@@ -662,49 +673,254 @@
     <t>+256700000002</t>
   </si>
   <si>
+    <t>tracy54321@email.com</t>
+  </si>
+  <si>
+    <t>2022-08-14 00:00:00</t>
+  </si>
+  <si>
     <t>ST-3</t>
   </si>
   <si>
     <t>James Bond</t>
   </si>
   <si>
+    <t>256777027429</t>
+  </si>
+  <si>
     <t>jamesbond7@email.com</t>
   </si>
   <si>
-    <t>tracy54321@email.com</t>
-  </si>
-  <si>
-    <t>alvarez89@email.com</t>
+    <t>2024-10-04 00:00:00</t>
+  </si>
+  <si>
+    <t>ST-4</t>
+  </si>
+  <si>
+    <t>256747839859</t>
+  </si>
+  <si>
+    <t>brian8gd@email.com</t>
   </si>
   <si>
     <t xml:space="preserve">James </t>
   </si>
   <si>
-    <t>ST-4</t>
-  </si>
-  <si>
-    <t>brian8gd@email.com</t>
+    <t>256774836282</t>
   </si>
   <si>
     <t>jamesss32@email.com</t>
+  </si>
+  <si>
+    <t>2024-09-04 00:00:00</t>
+  </si>
+  <si>
+    <t>staff_name</t>
+  </si>
+  <si>
+    <t>request_date</t>
+  </si>
+  <si>
+    <t>place_to_visit</t>
+  </si>
+  <si>
+    <t>purpose_of_visit</t>
+  </si>
+  <si>
+    <t>expected_outcome</t>
+  </si>
+  <si>
+    <t>amount_needed</t>
+  </si>
+  <si>
+    <t>hr_notes</t>
+  </si>
+  <si>
+    <t>approved_by</t>
+  </si>
+  <si>
+    <t>approved_date</t>
+  </si>
+  <si>
+    <t>decided_by</t>
+  </si>
+  <si>
+    <t>decided_date</t>
+  </si>
+  <si>
+    <t>estimated_time</t>
+  </si>
+  <si>
+    <t>actual_time</t>
+  </si>
+  <si>
+    <t>allowance_needed</t>
+  </si>
+  <si>
+    <t>report_submitted</t>
+  </si>
+  <si>
+    <t>report_notes</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>payment_status</t>
+  </si>
+  <si>
+    <t>actual_time_spent</t>
+  </si>
+  <si>
+    <t>FT-4B3710AB</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>Wandegeya</t>
+  </si>
+  <si>
+    <t>40 minutes</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>FT-0F00B3E3</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>30000</t>
+  </si>
+  <si>
+    <t>period_type</t>
+  </si>
+  <si>
+    <t>period_start</t>
+  </si>
+  <si>
+    <t>metric</t>
+  </si>
+  <si>
+    <t>target_value</t>
+  </si>
+  <si>
+    <t>set_by</t>
+  </si>
+  <si>
+    <t>date_set</t>
+  </si>
+  <si>
+    <t>person_name</t>
+  </si>
+  <si>
+    <t>TG-A92868A4</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>Sales Count</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>HumanResources</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>TG-4B54E541</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>Maintenance Count</t>
+  </si>
+  <si>
+    <t>task</t>
+  </si>
+  <si>
+    <t>date_created</t>
+  </si>
+  <si>
+    <t>T-C7245D98</t>
+  </si>
+  <si>
+    <t>Sending emails to the Sales team</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>T-1C590AB2</t>
+  </si>
+  <si>
+    <t>Giving out appraisal forms</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>T-40ACFF8F</t>
+  </si>
+  <si>
+    <t>Stamping forms</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>item_type</t>
+  </si>
+  <si>
+    <t>date_issued</t>
+  </si>
+  <si>
+    <t>returned</t>
+  </si>
+  <si>
+    <t>date_returned</t>
+  </si>
+  <si>
+    <t>AS-D5A8CF99</t>
+  </si>
+  <si>
+    <t>Business Card</t>
+  </si>
+  <si>
+    <t>Given business card</t>
+  </si>
+  <si>
+    <t>AS-C612B8C1</t>
+  </si>
+  <si>
+    <t>Uniform</t>
+  </si>
+  <si>
+    <t>given uniform</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -727,17 +943,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1200,6 +1412,392 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H1" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1" t="s">
+        <v>243</v>
+      </c>
+      <c r="J1" t="s">
+        <v>244</v>
+      </c>
+      <c r="K1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L1" t="s">
+        <v>246</v>
+      </c>
+      <c r="M1" t="s">
+        <v>170</v>
+      </c>
+      <c r="N1" t="s">
+        <v>247</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F2" t="s">
+        <v>251</v>
+      </c>
+      <c r="H2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I2" t="s">
+        <v>253</v>
+      </c>
+      <c r="K2" t="s">
+        <v>253</v>
+      </c>
+      <c r="L2" t="s">
+        <v>254</v>
+      </c>
+      <c r="O2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F3" t="s">
+        <v>251</v>
+      </c>
+      <c r="H3" t="s">
+        <v>257</v>
+      </c>
+      <c r="I3" t="s">
+        <v>253</v>
+      </c>
+      <c r="K3" t="s">
+        <v>253</v>
+      </c>
+      <c r="L3" t="s">
+        <v>254</v>
+      </c>
+      <c r="O3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G1" t="s">
+        <v>261</v>
+      </c>
+      <c r="H1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I1" t="s">
+        <v>263</v>
+      </c>
+      <c r="J1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F2" t="s">
+        <v>267</v>
+      </c>
+      <c r="G2" t="s">
+        <v>268</v>
+      </c>
+      <c r="H2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I2" t="s">
+        <v>270</v>
+      </c>
+      <c r="J2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>269</v>
+      </c>
+      <c r="I3" t="s">
+        <v>270</v>
+      </c>
+      <c r="J3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C4" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E1" t="s">
+        <v>287</v>
+      </c>
+      <c r="F1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J7"/>
@@ -1685,28 +2283,28 @@
         <v>134</v>
       </c>
       <c r="H3" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="I3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P3" t="s">
         <v>129</v>
@@ -1717,7 +2315,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -1732,10 +2330,10 @@
         <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H4" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="I4" t="s">
         <v>145</v>
@@ -1747,7 +2345,7 @@
         <v>126</v>
       </c>
       <c r="L4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M4" t="s">
         <v>146</v>
@@ -1788,10 +2386,10 @@
         <v>150</v>
       </c>
       <c r="J5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L5" t="s">
         <v>151</v>
@@ -1829,7 +2427,7 @@
         <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H6" t="s">
         <v>149</v>
@@ -1838,7 +2436,7 @@
         <v>150</v>
       </c>
       <c r="J6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K6" t="s">
         <v>156</v>
@@ -1888,7 +2486,7 @@
         <v>145</v>
       </c>
       <c r="J7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K7" t="s">
         <v>156</v>
@@ -1927,19 +2525,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" t="s">
         <v>166</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>167</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>168</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>169</v>
-      </c>
-      <c r="F1" t="s">
-        <v>170</v>
       </c>
       <c r="G1" t="s">
         <v>113</v>
@@ -1948,18 +2546,18 @@
         <v>5</v>
       </c>
       <c r="I1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J1" t="s">
         <v>112</v>
       </c>
       <c r="K1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B2" t="s">
         <v>131</v>
@@ -1968,24 +2566,24 @@
         <v>121</v>
       </c>
       <c r="D2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" t="s">
         <v>140</v>
       </c>
-      <c r="E2" t="s">
-        <v>139</v>
-      </c>
       <c r="F2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G2" t="s">
         <v>157</v>
       </c>
       <c r="H2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B3" t="s">
         <v>131</v>
@@ -1994,13 +2592,13 @@
         <v>24</v>
       </c>
       <c r="D3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E3" t="s">
         <v>177</v>
       </c>
-      <c r="E3" t="s">
+      <c r="H3" t="s">
         <v>178</v>
-      </c>
-      <c r="H3" t="s">
-        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -2018,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2027,24 +2625,24 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1" t="s">
         <v>181</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>182</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>183</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>184</v>
-      </c>
-      <c r="I1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B2" t="s">
         <v>29</v>
@@ -2056,42 +2654,42 @@
         <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F2" t="s">
         <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H2" t="s">
         <v>70</v>
       </c>
       <c r="I2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3" t="s">
         <v>190</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>191</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>192</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>193</v>
-      </c>
-      <c r="F3" t="s">
-        <v>194</v>
       </c>
       <c r="G3" t="s">
         <v>68</v>
       </c>
       <c r="H3" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="I3" t="s">
         <v>195</v>
@@ -2136,7 +2734,7 @@
         <v>201</v>
       </c>
       <c r="J1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K1" t="s">
         <v>202</v>
@@ -2156,7 +2754,7 @@
         <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F2" t="s">
         <v>70</v>
@@ -2168,7 +2766,7 @@
         <v>68</v>
       </c>
       <c r="J2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -2180,12 +2778,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="25.85546875" customWidth="1"/>
-    <col min="5" max="5" width="23.28515625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2220,101 +2812,148 @@
       <c r="D2" t="s">
         <v>209</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="F2" s="2">
-        <v>44137</v>
+      <c r="E2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F2" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E3" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3" t="s">
         <v>216</v>
-      </c>
-      <c r="F3" s="2">
-        <v>44787</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B4" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C4" t="s">
         <v>208</v>
       </c>
-      <c r="D4">
-        <v>256777027429</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F4" s="2">
-        <v>45569</v>
+      <c r="D4" t="s">
+        <v>219</v>
+      </c>
+      <c r="E4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F4" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C5" t="s">
-        <v>211</v>
-      </c>
-      <c r="D5">
-        <v>256747839859</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="F5" s="2">
-        <v>44787</v>
+        <v>213</v>
+      </c>
+      <c r="D5" t="s">
+        <v>223</v>
+      </c>
+      <c r="E5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F5" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B6" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D6">
-        <v>256774836282</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F6" s="2">
-        <v>45539</v>
+        <v>213</v>
+      </c>
+      <c r="D6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F6" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E2" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" t="s">
+        <v>235</v>
+      </c>
+      <c r="K1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1" t="s">
+        <v>237</v>
+      </c>
+      <c r="M1" t="s">
+        <v>238</v>
+      </c>
+      <c r="N1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>